--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139229</v>
       </c>
       <c r="B2" t="n">
-        <v>105732</v>
+        <v>105742</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121138797</v>
+        <v>121139153</v>
       </c>
       <c r="B3" t="n">
-        <v>58205</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,32 +802,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333048</v>
+        <v>332990</v>
       </c>
       <c r="R3" t="n">
-        <v>6403401</v>
+        <v>6403394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121139153</v>
+        <v>121138797</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>58208</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,32 +919,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>332990</v>
+        <v>333048</v>
       </c>
       <c r="R4" t="n">
-        <v>6403394</v>
+        <v>6403401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,11 +988,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139229</v>
+        <v>121139153</v>
       </c>
       <c r="B2" t="n">
-        <v>105742</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333092</v>
+        <v>332990</v>
       </c>
       <c r="R2" t="n">
-        <v>6403408</v>
+        <v>6403394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139153</v>
+        <v>121139229</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>105742</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,36 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332990</v>
+        <v>333092</v>
       </c>
       <c r="R3" t="n">
-        <v>6403394</v>
+        <v>6403408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,11 +876,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139153</v>
+        <v>121138797</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>58208</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332990</v>
+        <v>333048</v>
       </c>
       <c r="R2" t="n">
-        <v>6403394</v>
+        <v>6403401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +760,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139229</v>
+        <v>121139153</v>
       </c>
       <c r="B3" t="n">
-        <v>105742</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +799,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333092</v>
+        <v>332990</v>
       </c>
       <c r="R3" t="n">
-        <v>6403408</v>
+        <v>6403394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +872,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121138797</v>
+        <v>121139229</v>
       </c>
       <c r="B4" t="n">
-        <v>58208</v>
+        <v>105755</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,36 +916,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333048</v>
+        <v>333092</v>
       </c>
       <c r="R4" t="n">
-        <v>6403401</v>
+        <v>6403408</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121138797</v>
+        <v>121139153</v>
       </c>
       <c r="B2" t="n">
-        <v>58208</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333048</v>
+        <v>332990</v>
       </c>
       <c r="R2" t="n">
-        <v>6403401</v>
+        <v>6403394</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,6 +760,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139153</v>
+        <v>121138797</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>58208</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,32 +808,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332990</v>
+        <v>333048</v>
       </c>
       <c r="R3" t="n">
-        <v>6403394</v>
+        <v>6403401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +907,7 @@
         <v>121139229</v>
       </c>
       <c r="B4" t="n">
-        <v>105755</v>
+        <v>105756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121139153</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>8424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121138797</v>
+        <v>121139229</v>
       </c>
       <c r="B3" t="n">
-        <v>58208</v>
+        <v>105759</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,36 +804,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333048</v>
+        <v>333092</v>
       </c>
       <c r="R3" t="n">
-        <v>6403401</v>
+        <v>6403408</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121139229</v>
+        <v>121138797</v>
       </c>
       <c r="B4" t="n">
-        <v>105756</v>
+        <v>58211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +915,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333092</v>
+        <v>333048</v>
       </c>
       <c r="R4" t="n">
-        <v>6403408</v>
+        <v>6403401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139153</v>
+        <v>121139229</v>
       </c>
       <c r="B2" t="n">
-        <v>8424</v>
+        <v>105759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,36 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>332990</v>
+        <v>333092</v>
       </c>
       <c r="R2" t="n">
-        <v>6403394</v>
+        <v>6403408</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121139229</v>
+        <v>121139153</v>
       </c>
       <c r="B3" t="n">
-        <v>105759</v>
+        <v>8424</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,35 +798,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333092</v>
+        <v>332990</v>
       </c>
       <c r="R3" t="n">
-        <v>6403408</v>
+        <v>6403394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,6 +871,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,43 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121139229</v>
+        <v>121139130</v>
       </c>
       <c r="B2" t="n">
-        <v>105759</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333092</v>
+        <v>332812</v>
       </c>
       <c r="R2" t="n">
-        <v>6403408</v>
+        <v>6403368</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +768,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Elin Rostedt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -789,12 +789,7 @@
         <v>121139153</v>
       </c>
       <c r="B3" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,12 +901,7 @@
         <v>121138797</v>
       </c>
       <c r="B4" t="n">
-        <v>58211</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,6 +1003,323 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121139229</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lerum, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>333092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6403408</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121138859</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lerum, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>332814</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6403325</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum, Elin Rostedt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121138867</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lerum, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>333091</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6403403</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28233-2022 artfynd.xlsx
+++ b/artfynd/A 28233-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139130</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139153</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121138797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121139229</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121138859</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,8 +1349,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121138867</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>